--- a/BVSimulationFiles/65.xlsx
+++ b/BVSimulationFiles/65.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002334494773519164</v>
+        <v>0.004668989547038328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002344856042545388</v>
+        <v>0.004689712085090776</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002355217311571612</v>
+        <v>0.004710434623143224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002365578580597836</v>
+        <v>0.004731157161195672</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00237593984962406</v>
+        <v>0.00475187969924812</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002386301118650284</v>
+        <v>0.004772602237300568</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002396662387676508</v>
+        <v>0.004793324775353016</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002407023656702732</v>
+        <v>0.004814047313405464</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002417384925728956</v>
+        <v>0.004834769851457912</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00242774619475518</v>
+        <v>0.00485549238951036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002438107463781404</v>
+        <v>0.004876214927562808</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002448468732807628</v>
+        <v>0.004896937465615256</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002458830001833853</v>
+        <v>0.004917660003667706</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002469191270860077</v>
+        <v>0.004938382541720154</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0024795525398863</v>
+        <v>0.0049591050797726</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002489913808912525</v>
+        <v>0.00497982761782505</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002500275077938749</v>
+        <v>0.005000550155877498</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002510636346964973</v>
+        <v>0.005021272693929946</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002520997615991197</v>
+        <v>0.005041995231982394</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002531358885017421</v>
+        <v>0.005062717770034842</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002334494773519164</v>
+        <v>0.004668989547038328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002344856042545388</v>
+        <v>0.004689712085090776</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002355217311571612</v>
+        <v>0.004710434623143224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002365578580597836</v>
+        <v>0.004731157161195672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00237593984962406</v>
+        <v>0.00475187969924812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002386301118650284</v>
+        <v>0.004772602237300568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002396662387676508</v>
+        <v>0.004793324775353016</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002407023656702732</v>
+        <v>0.004814047313405464</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002417384925728956</v>
+        <v>0.004834769851457912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00242774619475518</v>
+        <v>0.00485549238951036</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002438107463781404</v>
+        <v>0.004876214927562808</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002448468732807628</v>
+        <v>0.004896937465615256</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002458830001833853</v>
+        <v>0.004917660003667706</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002469191270860077</v>
+        <v>0.004938382541720154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0024795525398863</v>
+        <v>0.0049591050797726</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002489913808912525</v>
+        <v>0.00497982761782505</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002500275077938749</v>
+        <v>0.005000550155877498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002510636346964973</v>
+        <v>0.005021272693929946</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002520997615991197</v>
+        <v>0.005041995231982394</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002531358885017421</v>
+        <v>0.005062717770034842</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/65.xlsx
+++ b/BVSimulationFiles/65.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004668989547038328</v>
+        <v>0.04668989547038328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004689712085090776</v>
+        <v>0.04689712085090776</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004710434623143224</v>
+        <v>0.04710434623143224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004731157161195672</v>
+        <v>0.04731157161195672</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00475187969924812</v>
+        <v>0.0475187969924812</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004772602237300568</v>
+        <v>0.04772602237300568</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004793324775353016</v>
+        <v>0.04793324775353016</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004814047313405464</v>
+        <v>0.04814047313405464</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004834769851457912</v>
+        <v>0.04834769851457912</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00485549238951036</v>
+        <v>0.0485549238951036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004876214927562808</v>
+        <v>0.04876214927562808</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004896937465615256</v>
+        <v>0.04896937465615256</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004917660003667706</v>
+        <v>0.04917660003667706</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004938382541720154</v>
+        <v>0.04938382541720154</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0049591050797726</v>
+        <v>0.049591050797726</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00497982761782505</v>
+        <v>0.0497982761782505</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005000550155877498</v>
+        <v>0.05000550155877498</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005021272693929946</v>
+        <v>0.05021272693929946</v>
       </c>
       <c r="T2" t="n">
-        <v>0.005041995231982394</v>
+        <v>0.05041995231982394</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005062717770034842</v>
+        <v>0.05062717770034842</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004668989547038328</v>
+        <v>0.04668989547038328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004689712085090776</v>
+        <v>0.04689712085090776</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004710434623143224</v>
+        <v>0.04710434623143224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004731157161195672</v>
+        <v>0.04731157161195672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00475187969924812</v>
+        <v>0.0475187969924812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004772602237300568</v>
+        <v>0.04772602237300568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004793324775353016</v>
+        <v>0.04793324775353016</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004814047313405464</v>
+        <v>0.04814047313405464</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004834769851457912</v>
+        <v>0.04834769851457912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00485549238951036</v>
+        <v>0.0485549238951036</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004876214927562808</v>
+        <v>0.04876214927562808</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004896937465615256</v>
+        <v>0.04896937465615256</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004917660003667706</v>
+        <v>0.04917660003667706</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004938382541720154</v>
+        <v>0.04938382541720154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0049591050797726</v>
+        <v>0.049591050797726</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00497982761782505</v>
+        <v>0.0497982761782505</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005000550155877498</v>
+        <v>0.05000550155877498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005021272693929946</v>
+        <v>0.05021272693929946</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005041995231982394</v>
+        <v>0.05041995231982394</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005062717770034842</v>
+        <v>0.05062717770034842</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/65.xlsx
+++ b/BVSimulationFiles/65.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04668989547038328</v>
+        <v>0.2589173399496651</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04689712085090776</v>
+        <v>0.2600665017491275</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04710434623143224</v>
+        <v>0.2612156635485899</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04731157161195672</v>
+        <v>0.2623648253480523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0475187969924812</v>
+        <v>0.2635139871475147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04772602237300568</v>
+        <v>0.2646631489469771</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04793324775353016</v>
+        <v>0.2658123107464394</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04814047313405464</v>
+        <v>0.2669614725459018</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04834769851457912</v>
+        <v>0.2681106343453642</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0485549238951036</v>
+        <v>0.2692597961448266</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04876214927562808</v>
+        <v>0.2704089579442889</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04896937465615256</v>
+        <v>0.2715581197437513</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04917660003667706</v>
+        <v>0.2727072815432137</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04938382541720154</v>
+        <v>0.2738564433426761</v>
       </c>
       <c r="P2" t="n">
-        <v>0.049591050797726</v>
+        <v>0.2750056051421385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0497982761782505</v>
+        <v>0.2761547669416008</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05000550155877498</v>
+        <v>0.2773039287410632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05021272693929946</v>
+        <v>0.2784530905405256</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05041995231982394</v>
+        <v>0.2796022523399879</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05062717770034842</v>
+        <v>0.2807514141394503</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04668989547038328</v>
+        <v>0.2589173399496651</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04689712085090776</v>
+        <v>0.2600665017491275</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04710434623143224</v>
+        <v>0.2612156635485899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04731157161195672</v>
+        <v>0.2623648253480523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0475187969924812</v>
+        <v>0.2635139871475147</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04772602237300568</v>
+        <v>0.2646631489469771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04793324775353016</v>
+        <v>0.2658123107464394</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04814047313405464</v>
+        <v>0.2669614725459018</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04834769851457912</v>
+        <v>0.2681106343453642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0485549238951036</v>
+        <v>0.2692597961448266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04876214927562808</v>
+        <v>0.2704089579442889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04896937465615256</v>
+        <v>0.2715581197437513</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04917660003667706</v>
+        <v>0.2727072815432137</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04938382541720154</v>
+        <v>0.2738564433426761</v>
       </c>
       <c r="P3" t="n">
-        <v>0.049591050797726</v>
+        <v>0.2750056051421385</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0497982761782505</v>
+        <v>0.2761547669416008</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05000550155877498</v>
+        <v>0.2773039287410632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05021272693929946</v>
+        <v>0.2784530905405256</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05041995231982394</v>
+        <v>0.2796022523399879</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05062717770034842</v>
+        <v>0.2807514141394503</v>
       </c>
     </row>
   </sheetData>
